--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
@@ -339,11 +339,11 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Painel'!$A$10:$A$33</f>
+              <f>'Painel'!$A$10:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Painel'!$D$10:$D$33</f>
+              <f>'Painel'!$D$10:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -588,12 +588,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Painel'!$A$10:$A$33</f>
+              <f>'Painel'!$A$10:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Painel'!$J$10:$J$33</f>
+              <f>'Painel'!$J$10:$J$39</f>
             </numRef>
           </val>
         </ser>
@@ -988,7 +988,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, digite a meta em meses de custo fixo (3 é um bom começo), o custo fixo dos últimos 3 meses com pró-labore (copie do Painel da planilha 09), o saldo em caixa, os compromissos ainda não pagos, o que já está guardado numa conta separada e o aporte mensal que cabe.</t>
+          <t>Em Config, digite a meta em meses (3 é um bom começo) e, para os últimos 3 meses, o custo fixo + pró-labore de cada um, copiado de "Para onde foi o dinheiro" no Painel da planilha 09 (as oito linhas de custo fixo mais a linha "Pró-labore dos sócios"). Depois o saldo em caixa, os compromissos ainda não pagos, o que já está guardado numa conta separada e o aporte mensal que cabe.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Toda sexta, 5 minutos: atualizar o valor atual das metas. No fechamento do mês: transferir o aporte para a conta da reserva e atualizar o saldo e o custo fixo em Config.</t>
+          <t>É uma planilha MENSAL, não entra nos 30 minutos semanais da planilha 03: no fechamento de cada mês, 10 minutos para transferir o aporte para a conta da reserva, atualizar o saldo, o custo fixo + pró-labore e o valor atual das três metas em Config.</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1198,7 +1198,7 @@
       <c r="F4" s="12" t="n"/>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Meses de custo fixo cobertos</t>
+          <t>Meses de custo fixo + pró-labore cobertos</t>
         </is>
       </c>
       <c r="H4" s="14" t="n"/>
@@ -1212,7 +1212,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>Config!$B$8*Config!$B$16</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
@@ -1222,17 +1222,17 @@
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>MAX(0,A5-C5)</f>
-        <v>70000</v>
+        <v>75197</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>IF(Config!$B$16=0,0,C5/Config!$B$16)</f>
-        <v>0.5</v>
+        <v>0.470867854300033</v>
       </c>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="19" t="str">
-        <f>IF(C5&gt;=A5,"Já atingida",IFERROR(INDEX(A10:A33,MATCH("Meta atingida",F10:F33,0)),"Depois de 24 meses"))</f>
-        <v>Setembro/2028</v>
+        <f>IF(C5&gt;=A5,"Já atingida",IFERROR(INDEX(A10:A39,MATCH("Meta atingida",F10:F39,0)),"Depois de 24 meses"))</f>
+        <v>Novembro/2028</v>
       </c>
       <c r="J5" s="8" t="n"/>
     </row>
@@ -1244,12 +1244,12 @@
         </is>
       </c>
       <c r="B7" s="21" t="str">
-        <f>IF(G5&lt;1,"Vermelho: menos de 1 mês de custo fixo guardado",IF(G5&lt;Config!$B$8,"Amarelo: abaixo da meta",IF(G5&lt;Config!$B$8+1,"Verde: meta atingida","Verde: acima da meta")))</f>
-        <v>Vermelho: menos de 1 mês de custo fixo guardado</v>
+        <f>IF(G5&lt;1,"Vermelho: menos de 1 mês de custo fixo + pró-labore guardado",IF(G5&lt;Config!$B$8,"Amarelo: abaixo da meta",IF(G5&lt;Config!$B$8+1,"Verde: meta atingida","Verde: acima da meta")))</f>
+        <v>Vermelho: menos de 1 mês de custo fixo + pró-labore guardado</v>
       </c>
       <c r="G7" s="22" t="str">
         <f>"Contando o caixa livre (R$ "&amp;FIXED(Config!$B$21,0)&amp;"): "&amp;FIXED(IF(Config!$B$16=0,0,(C5+Config!$B$21)/Config!$B$16),1)&amp;" meses"</f>
-        <v>Contando o caixa livre (R$ 26,254): 1.4 meses</v>
+        <v>Contando o caixa livre (R$ 26,836): 1.4 meses</v>
       </c>
     </row>
     <row r="8">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E10" s="30">
         <f>IF($A$5=0,"",D10/$A$5)</f>
-        <v>0.202380952380952</v>
+        <v>0.190589369597632</v>
       </c>
       <c r="F10" s="31">
         <f>IF(D10&gt;=$A$5,IF(B10&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1331,7 +1331,7 @@
       <c r="I10" s="26" t="n"/>
       <c r="J10" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="11">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="E11" s="30">
         <f>IF($A$5=0,"",D11/$A$5)</f>
-        <v>0.238095238095238</v>
+        <v>0.22422278776192</v>
       </c>
       <c r="F11" s="31">
         <f>IF(D11&gt;=$A$5,IF(B11&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1367,7 +1367,7 @@
       <c r="I11" s="26" t="n"/>
       <c r="J11" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="12">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E12" s="30">
         <f>IF($A$5=0,"",D12/$A$5)</f>
-        <v>0.273809523809524</v>
+        <v>0.257856205926208</v>
       </c>
       <c r="F12" s="31">
         <f>IF(D12&gt;=$A$5,IF(B12&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1403,7 +1403,7 @@
       <c r="I12" s="26" t="n"/>
       <c r="J12" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="13">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E13" s="30">
         <f>IF($A$5=0,"",D13/$A$5)</f>
-        <v>0.30952380952381</v>
+        <v>0.291489624090496</v>
       </c>
       <c r="F13" s="31">
         <f>IF(D13&gt;=$A$5,IF(B13&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1439,7 +1439,7 @@
       <c r="I13" s="26" t="n"/>
       <c r="J13" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="14">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E14" s="30">
         <f>IF($A$5=0,"",D14/$A$5)</f>
-        <v>0.345238095238095</v>
+        <v>0.325123042254784</v>
       </c>
       <c r="F14" s="31">
         <f>IF(D14&gt;=$A$5,IF(B14&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1475,7 +1475,7 @@
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="15">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E15" s="30">
         <f>IF($A$5=0,"",D15/$A$5)</f>
-        <v>0.380952380952381</v>
+        <v>0.358756460419072</v>
       </c>
       <c r="F15" s="31">
         <f>IF(D15&gt;=$A$5,IF(B15&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1511,7 +1511,7 @@
       <c r="I15" s="26" t="n"/>
       <c r="J15" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="16">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="E16" s="30">
         <f>IF($A$5=0,"",D16/$A$5)</f>
-        <v>0.416666666666667</v>
+        <v>0.39238987858336</v>
       </c>
       <c r="F16" s="31">
         <f>IF(D16&gt;=$A$5,IF(B16&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1541,13 +1541,13 @@
       </c>
       <c r="G16" s="32" t="str">
         <f>IF(E16="","",REPT("█",ROUND(MIN(1,E16)*30,0)))</f>
-        <v>█████████████</v>
+        <v>████████████</v>
       </c>
       <c r="H16" s="25" t="n"/>
       <c r="I16" s="26" t="n"/>
       <c r="J16" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="17">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E17" s="30">
         <f>IF($A$5=0,"",D17/$A$5)</f>
-        <v>0.452380952380952</v>
+        <v>0.426023296747648</v>
       </c>
       <c r="F17" s="31">
         <f>IF(D17&gt;=$A$5,IF(B17&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1577,13 +1577,13 @@
       </c>
       <c r="G17" s="32" t="str">
         <f>IF(E17="","",REPT("█",ROUND(MIN(1,E17)*30,0)))</f>
-        <v>██████████████</v>
+        <v>█████████████</v>
       </c>
       <c r="H17" s="25" t="n"/>
       <c r="I17" s="26" t="n"/>
       <c r="J17" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="18">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E18" s="30">
         <f>IF($A$5=0,"",D18/$A$5)</f>
-        <v>0.488095238095238</v>
+        <v>0.459656714911937</v>
       </c>
       <c r="F18" s="31">
         <f>IF(D18&gt;=$A$5,IF(B18&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1613,13 +1613,13 @@
       </c>
       <c r="G18" s="32" t="str">
         <f>IF(E18="","",REPT("█",ROUND(MIN(1,E18)*30,0)))</f>
-        <v>███████████████</v>
+        <v>██████████████</v>
       </c>
       <c r="H18" s="25" t="n"/>
       <c r="I18" s="26" t="n"/>
       <c r="J18" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="19">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E19" s="30">
         <f>IF($A$5=0,"",D19/$A$5)</f>
-        <v>0.523809523809524</v>
+        <v>0.493290133076225</v>
       </c>
       <c r="F19" s="31">
         <f>IF(D19&gt;=$A$5,IF(B19&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1649,13 +1649,13 @@
       </c>
       <c r="G19" s="32" t="str">
         <f>IF(E19="","",REPT("█",ROUND(MIN(1,E19)*30,0)))</f>
-        <v>████████████████</v>
+        <v>███████████████</v>
       </c>
       <c r="H19" s="25" t="n"/>
       <c r="I19" s="26" t="n"/>
       <c r="J19" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="20">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E20" s="30">
         <f>IF($A$5=0,"",D20/$A$5)</f>
-        <v>0.55952380952381</v>
+        <v>0.526923551240513</v>
       </c>
       <c r="F20" s="31">
         <f>IF(D20&gt;=$A$5,IF(B20&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1685,13 +1685,13 @@
       </c>
       <c r="G20" s="32" t="str">
         <f>IF(E20="","",REPT("█",ROUND(MIN(1,E20)*30,0)))</f>
-        <v>█████████████████</v>
+        <v>████████████████</v>
       </c>
       <c r="H20" s="25" t="n"/>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="21">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E21" s="30">
         <f>IF($A$5=0,"",D21/$A$5)</f>
-        <v>0.595238095238095</v>
+        <v>0.560556969404801</v>
       </c>
       <c r="F21" s="31">
         <f>IF(D21&gt;=$A$5,IF(B21&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1721,13 +1721,13 @@
       </c>
       <c r="G21" s="32" t="str">
         <f>IF(E21="","",REPT("█",ROUND(MIN(1,E21)*30,0)))</f>
-        <v>██████████████████</v>
+        <v>█████████████████</v>
       </c>
       <c r="H21" s="25" t="n"/>
       <c r="I21" s="26" t="n"/>
       <c r="J21" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="22">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E22" s="30">
         <f>IF($A$5=0,"",D22/$A$5)</f>
-        <v>0.630952380952381</v>
+        <v>0.594190387569089</v>
       </c>
       <c r="F22" s="31">
         <f>IF(D22&gt;=$A$5,IF(B22&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1757,13 +1757,13 @@
       </c>
       <c r="G22" s="32" t="str">
         <f>IF(E22="","",REPT("█",ROUND(MIN(1,E22)*30,0)))</f>
-        <v>███████████████████</v>
+        <v>██████████████████</v>
       </c>
       <c r="H22" s="25" t="n"/>
       <c r="I22" s="26" t="n"/>
       <c r="J22" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="23">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E23" s="30">
         <f>IF($A$5=0,"",D23/$A$5)</f>
-        <v>0.666666666666667</v>
+        <v>0.627823805733377</v>
       </c>
       <c r="F23" s="31">
         <f>IF(D23&gt;=$A$5,IF(B23&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1793,13 +1793,13 @@
       </c>
       <c r="G23" s="32" t="str">
         <f>IF(E23="","",REPT("█",ROUND(MIN(1,E23)*30,0)))</f>
-        <v>████████████████████</v>
+        <v>███████████████████</v>
       </c>
       <c r="H23" s="25" t="n"/>
       <c r="I23" s="26" t="n"/>
       <c r="J23" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="24">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E24" s="30">
         <f>IF($A$5=0,"",D24/$A$5)</f>
-        <v>0.702380952380952</v>
+        <v>0.661457223897665</v>
       </c>
       <c r="F24" s="31">
         <f>IF(D24&gt;=$A$5,IF(B24&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1829,13 +1829,13 @@
       </c>
       <c r="G24" s="32" t="str">
         <f>IF(E24="","",REPT("█",ROUND(MIN(1,E24)*30,0)))</f>
-        <v>█████████████████████</v>
+        <v>████████████████████</v>
       </c>
       <c r="H24" s="25" t="n"/>
       <c r="I24" s="26" t="n"/>
       <c r="J24" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="25">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="E25" s="30">
         <f>IF($A$5=0,"",D25/$A$5)</f>
-        <v>0.738095238095238</v>
+        <v>0.695090642061953</v>
       </c>
       <c r="F25" s="31">
         <f>IF(D25&gt;=$A$5,IF(B25&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1865,13 +1865,13 @@
       </c>
       <c r="G25" s="32" t="str">
         <f>IF(E25="","",REPT("█",ROUND(MIN(1,E25)*30,0)))</f>
-        <v>██████████████████████</v>
+        <v>█████████████████████</v>
       </c>
       <c r="H25" s="25" t="n"/>
       <c r="I25" s="26" t="n"/>
       <c r="J25" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="26">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E26" s="30">
         <f>IF($A$5=0,"",D26/$A$5)</f>
-        <v>0.773809523809524</v>
+        <v>0.728724060226241</v>
       </c>
       <c r="F26" s="31">
         <f>IF(D26&gt;=$A$5,IF(B26&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1901,13 +1901,13 @@
       </c>
       <c r="G26" s="32" t="str">
         <f>IF(E26="","",REPT("█",ROUND(MIN(1,E26)*30,0)))</f>
-        <v>███████████████████████</v>
+        <v>██████████████████████</v>
       </c>
       <c r="H26" s="25" t="n"/>
       <c r="I26" s="26" t="n"/>
       <c r="J26" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="27">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E27" s="30">
         <f>IF($A$5=0,"",D27/$A$5)</f>
-        <v>0.80952380952381</v>
+        <v>0.762357478390529</v>
       </c>
       <c r="F27" s="31">
         <f>IF(D27&gt;=$A$5,IF(B27&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1937,13 +1937,13 @@
       </c>
       <c r="G27" s="32" t="str">
         <f>IF(E27="","",REPT("█",ROUND(MIN(1,E27)*30,0)))</f>
-        <v>████████████████████████</v>
+        <v>███████████████████████</v>
       </c>
       <c r="H27" s="25" t="n"/>
       <c r="I27" s="26" t="n"/>
       <c r="J27" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="28">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E28" s="30">
         <f>IF($A$5=0,"",D28/$A$5)</f>
-        <v>0.845238095238095</v>
+        <v>0.795990896554817</v>
       </c>
       <c r="F28" s="31">
         <f>IF(D28&gt;=$A$5,IF(B28&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1973,13 +1973,13 @@
       </c>
       <c r="G28" s="32" t="str">
         <f>IF(E28="","",REPT("█",ROUND(MIN(1,E28)*30,0)))</f>
-        <v>█████████████████████████</v>
+        <v>████████████████████████</v>
       </c>
       <c r="H28" s="25" t="n"/>
       <c r="I28" s="26" t="n"/>
       <c r="J28" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="29">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E29" s="30">
         <f>IF($A$5=0,"",D29/$A$5)</f>
-        <v>0.880952380952381</v>
+        <v>0.829624314719105</v>
       </c>
       <c r="F29" s="31">
         <f>IF(D29&gt;=$A$5,IF(B29&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2009,13 +2009,13 @@
       </c>
       <c r="G29" s="32" t="str">
         <f>IF(E29="","",REPT("█",ROUND(MIN(1,E29)*30,0)))</f>
-        <v>██████████████████████████</v>
+        <v>█████████████████████████</v>
       </c>
       <c r="H29" s="25" t="n"/>
       <c r="I29" s="26" t="n"/>
       <c r="J29" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="30">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E30" s="30">
         <f>IF($A$5=0,"",D30/$A$5)</f>
-        <v>0.916666666666667</v>
+        <v>0.863257732883393</v>
       </c>
       <c r="F30" s="31">
         <f>IF(D30&gt;=$A$5,IF(B30&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2045,13 +2045,13 @@
       </c>
       <c r="G30" s="32" t="str">
         <f>IF(E30="","",REPT("█",ROUND(MIN(1,E30)*30,0)))</f>
-        <v>████████████████████████████</v>
+        <v>██████████████████████████</v>
       </c>
       <c r="H30" s="25" t="n"/>
       <c r="I30" s="26" t="n"/>
       <c r="J30" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="31">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E31" s="30">
         <f>IF($A$5=0,"",D31/$A$5)</f>
-        <v>0.952380952380952</v>
+        <v>0.896891151047681</v>
       </c>
       <c r="F31" s="31">
         <f>IF(D31&gt;=$A$5,IF(B31&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2081,13 +2081,13 @@
       </c>
       <c r="G31" s="32" t="str">
         <f>IF(E31="","",REPT("█",ROUND(MIN(1,E31)*30,0)))</f>
-        <v>█████████████████████████████</v>
+        <v>███████████████████████████</v>
       </c>
       <c r="H31" s="25" t="n"/>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="32">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E32" s="30">
         <f>IF($A$5=0,"",D32/$A$5)</f>
-        <v>0.988095238095238</v>
+        <v>0.930524569211969</v>
       </c>
       <c r="F32" s="31">
         <f>IF(D32&gt;=$A$5,IF(B32&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2117,13 +2117,13 @@
       </c>
       <c r="G32" s="32" t="str">
         <f>IF(E32="","",REPT("█",ROUND(MIN(1,E32)*30,0)))</f>
-        <v>██████████████████████████████</v>
+        <v>████████████████████████████</v>
       </c>
       <c r="H32" s="25" t="n"/>
       <c r="I32" s="26" t="n"/>
       <c r="J32" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="33">
@@ -2145,183 +2145,399 @@
       </c>
       <c r="E33" s="30">
         <f>IF($A$5=0,"",D33/$A$5)</f>
-        <v>1.02380952380952</v>
-      </c>
-      <c r="F33" s="31" t="str">
+        <v>0.964157987376257</v>
+      </c>
+      <c r="F33" s="31">
         <f>IF(D33&gt;=$A$5,IF(B33&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v>Meta atingida</v>
+        <v/>
       </c>
       <c r="G33" s="32" t="str">
         <f>IF(E33="","",REPT("█",ROUND(MIN(1,E33)*30,0)))</f>
-        <v>██████████████████████████████</v>
+        <v>█████████████████████████████</v>
       </c>
       <c r="H33" s="25" t="n"/>
       <c r="I33" s="26" t="n"/>
       <c r="J33" s="33">
         <f>$A$5</f>
-        <v>84000</v>
+        <v>89197</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="27" t="str">
+        <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+24-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+24-1)/12))</f>
+        <v>Outubro/2028</v>
+      </c>
+      <c r="B34" s="28">
+        <f>D33</f>
+        <v>86000</v>
+      </c>
+      <c r="C34" s="28">
+        <f>Config!$B$9</f>
+        <v>3000</v>
+      </c>
+      <c r="D34" s="29">
+        <f>B34+C34</f>
+        <v>89000</v>
+      </c>
+      <c r="E34" s="30">
+        <f>IF($A$5=0,"",D34/$A$5)</f>
+        <v>0.997791405540545</v>
+      </c>
+      <c r="F34" s="31">
+        <f>IF(D34&gt;=$A$5,IF(B34&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="32" t="str">
+        <f>IF(E34="","",REPT("█",ROUND(MIN(1,E34)*30,0)))</f>
+        <v>██████████████████████████████</v>
+      </c>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="26" t="n"/>
+      <c r="J34" s="33">
+        <f>$A$5</f>
+        <v>89197</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="str">
+        <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+25-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+25-1)/12))</f>
+        <v>Novembro/2028</v>
+      </c>
+      <c r="B35" s="28">
+        <f>D34</f>
+        <v>89000</v>
+      </c>
+      <c r="C35" s="28">
+        <f>Config!$B$9</f>
+        <v>3000</v>
+      </c>
+      <c r="D35" s="29">
+        <f>B35+C35</f>
+        <v>92000</v>
+      </c>
+      <c r="E35" s="30">
+        <f>IF($A$5=0,"",D35/$A$5)</f>
+        <v>1.03142482370483</v>
+      </c>
+      <c r="F35" s="31" t="str">
+        <f>IF(D35&gt;=$A$5,IF(B35&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
+        <v>Meta atingida</v>
+      </c>
+      <c r="G35" s="32" t="str">
+        <f>IF(E35="","",REPT("█",ROUND(MIN(1,E35)*30,0)))</f>
+        <v>██████████████████████████████</v>
+      </c>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="26" t="n"/>
+      <c r="J35" s="33">
+        <f>$A$5</f>
+        <v>89197</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="str">
+        <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+26-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+26-1)/12))</f>
+        <v>Dezembro/2028</v>
+      </c>
+      <c r="B36" s="28">
+        <f>D35</f>
+        <v>92000</v>
+      </c>
+      <c r="C36" s="28">
+        <f>Config!$B$9</f>
+        <v>3000</v>
+      </c>
+      <c r="D36" s="29">
+        <f>B36+C36</f>
+        <v>95000</v>
+      </c>
+      <c r="E36" s="30">
+        <f>IF($A$5=0,"",D36/$A$5)</f>
+        <v>1.06505824186912</v>
+      </c>
+      <c r="F36" s="31" t="str">
+        <f>IF(D36&gt;=$A$5,IF(B36&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
+        <v>Acima da meta</v>
+      </c>
+      <c r="G36" s="32" t="str">
+        <f>IF(E36="","",REPT("█",ROUND(MIN(1,E36)*30,0)))</f>
+        <v>██████████████████████████████</v>
+      </c>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="26" t="n"/>
+      <c r="J36" s="33">
+        <f>$A$5</f>
+        <v>89197</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="27" t="str">
+        <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+27-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+27-1)/12))</f>
+        <v>Janeiro/2029</v>
+      </c>
+      <c r="B37" s="28">
+        <f>D36</f>
+        <v>95000</v>
+      </c>
+      <c r="C37" s="28">
+        <f>Config!$B$9</f>
+        <v>3000</v>
+      </c>
+      <c r="D37" s="29">
+        <f>B37+C37</f>
+        <v>98000</v>
+      </c>
+      <c r="E37" s="30">
+        <f>IF($A$5=0,"",D37/$A$5)</f>
+        <v>1.09869166003341</v>
+      </c>
+      <c r="F37" s="31" t="str">
+        <f>IF(D37&gt;=$A$5,IF(B37&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
+        <v>Acima da meta</v>
+      </c>
+      <c r="G37" s="32" t="str">
+        <f>IF(E37="","",REPT("█",ROUND(MIN(1,E37)*30,0)))</f>
+        <v>██████████████████████████████</v>
+      </c>
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="26" t="n"/>
+      <c r="J37" s="33">
+        <f>$A$5</f>
+        <v>89197</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="27" t="str">
+        <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+28-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+28-1)/12))</f>
+        <v>Fevereiro/2029</v>
+      </c>
+      <c r="B38" s="28">
+        <f>D37</f>
+        <v>98000</v>
+      </c>
+      <c r="C38" s="28">
+        <f>Config!$B$9</f>
+        <v>3000</v>
+      </c>
+      <c r="D38" s="29">
+        <f>B38+C38</f>
+        <v>101000</v>
+      </c>
+      <c r="E38" s="30">
+        <f>IF($A$5=0,"",D38/$A$5)</f>
+        <v>1.1323250781977</v>
+      </c>
+      <c r="F38" s="31" t="str">
+        <f>IF(D38&gt;=$A$5,IF(B38&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
+        <v>Acima da meta</v>
+      </c>
+      <c r="G38" s="32" t="str">
+        <f>IF(E38="","",REPT("█",ROUND(MIN(1,E38)*30,0)))</f>
+        <v>██████████████████████████████</v>
+      </c>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="26" t="n"/>
+      <c r="J38" s="33">
+        <f>$A$5</f>
+        <v>89197</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="str">
+        <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+29-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+29-1)/12))</f>
+        <v>Março/2029</v>
+      </c>
+      <c r="B39" s="28">
+        <f>D38</f>
+        <v>101000</v>
+      </c>
+      <c r="C39" s="28">
+        <f>Config!$B$9</f>
+        <v>3000</v>
+      </c>
+      <c r="D39" s="29">
+        <f>B39+C39</f>
+        <v>104000</v>
+      </c>
+      <c r="E39" s="30">
+        <f>IF($A$5=0,"",D39/$A$5)</f>
+        <v>1.16595849636199</v>
+      </c>
+      <c r="F39" s="31" t="str">
+        <f>IF(D39&gt;=$A$5,IF(B39&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
+        <v>Acima da meta</v>
+      </c>
+      <c r="G39" s="32" t="str">
+        <f>IF(E39="","",REPT("█",ROUND(MIN(1,E39)*30,0)))</f>
+        <v>██████████████████████████████</v>
+      </c>
+      <c r="H39" s="25" t="n"/>
+      <c r="I39" s="26" t="n"/>
+      <c r="J39" s="33">
+        <f>$A$5</f>
+        <v>89197</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>Aporte igual todo mês, sem rendimento. Quando a reserva bater a meta, decida com o sócio o que fazer com o aporte: manter, reduzir ou virar distribuição.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Metas de caixa do trimestre</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>Valor alvo</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>Valor atual</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>Progresso</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="F36" s="24" t="inlineStr">
+      <c r="F42" s="24" t="inlineStr">
         <is>
           <t>Prazo</t>
         </is>
       </c>
-      <c r="G36" s="24" t="inlineStr">
+      <c r="G42" s="24" t="inlineStr">
         <is>
           <t>Dias restantes</t>
         </is>
       </c>
-      <c r="H36" s="24" t="inlineStr">
+      <c r="H42" s="24" t="inlineStr">
         <is>
           <t>Situação</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="35" t="str">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="35" t="str">
         <f>IF(Config!$A$26="","",Config!$A$26)</f>
-        <v>Reserva com 1 mês de custo fixo</v>
-      </c>
-      <c r="B37" s="28">
+        <v>Reserva com 1 mês de custo fixo + pró-labore</v>
+      </c>
+      <c r="B43" s="28">
         <f>IF(Config!$A$26="","",Config!$B$26)</f>
         <v>28000</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C43" s="28">
         <f>IF(Config!$A$26="","",Config!$C$26)</f>
         <v>14000</v>
       </c>
-      <c r="D37" s="30">
-        <f>IF(OR(Config!$A$26="",B37=0),"",MIN(1,C37/B37))</f>
+      <c r="D43" s="30">
+        <f>IF(OR(Config!$A$26="",B43=0),"",MIN(1,C43/B43))</f>
         <v>0.5</v>
       </c>
-      <c r="E37" s="32" t="str">
-        <f>IF(D37="","",REPT("█",ROUND(D37*20,0)))</f>
+      <c r="E43" s="32" t="str">
+        <f>IF(D43="","",REPT("█",ROUND(D43*20,0)))</f>
         <v>██████████</v>
       </c>
-      <c r="F37" s="36">
+      <c r="F43" s="36">
         <f>IF(OR(Config!$A$26="",Config!$D$26=""),"",Config!$D$26)</f>
         <v>46387.0</v>
       </c>
-      <c r="G37" s="37">
-        <f>IF(OR(Config!$A$26="",F37="",H37="Concluída"),"",F37-Config!$B$5)</f>
+      <c r="G43" s="37">
+        <f>IF(OR(Config!$A$26="",F43="",H43="Concluída"),"",F43-Config!$B$5)</f>
         <v>108</v>
       </c>
-      <c r="H37" s="31" t="str">
-        <f>IF(Config!$A$26="","",IF(AND(B37&gt;0,C37&gt;=B37),"Concluída",IF(AND(F37&lt;&gt;"",F37&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
+      <c r="H43" s="31" t="str">
+        <f>IF(Config!$A$26="","",IF(AND(B43&gt;0,C43&gt;=B43),"Concluída",IF(AND(F43&lt;&gt;"",F43&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
         <v>Em andamento</v>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="35" t="str">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="35" t="str">
         <f>IF(Config!$A$27="","",Config!$A$27)</f>
         <v>Receber R$ 130.000 no trimestre</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B44" s="28">
         <f>IF(Config!$A$27="","",Config!$B$27)</f>
         <v>130000</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C44" s="28">
         <f>IF(Config!$A$27="","",Config!$C$27)</f>
-        <v>125007</v>
-      </c>
-      <c r="D38" s="30">
-        <f>IF(OR(Config!$A$27="",B38=0),"",MIN(1,C38/B38))</f>
-        <v>0.961592307692308</v>
-      </c>
-      <c r="E38" s="32" t="str">
-        <f>IF(D38="","",REPT("█",ROUND(D38*20,0)))</f>
+        <v>125032</v>
+      </c>
+      <c r="D44" s="30">
+        <f>IF(OR(Config!$A$27="",B44=0),"",MIN(1,C44/B44))</f>
+        <v>0.961784615384615</v>
+      </c>
+      <c r="E44" s="32" t="str">
+        <f>IF(D44="","",REPT("█",ROUND(D44*20,0)))</f>
         <v>███████████████████</v>
       </c>
-      <c r="F38" s="36">
+      <c r="F44" s="36">
         <f>IF(OR(Config!$A$27="",Config!$D$27=""),"",Config!$D$27)</f>
         <v>46295.0</v>
       </c>
-      <c r="G38" s="37">
-        <f>IF(OR(Config!$A$27="",F38="",H38="Concluída"),"",F38-Config!$B$5)</f>
+      <c r="G44" s="37">
+        <f>IF(OR(Config!$A$27="",F44="",H44="Concluída"),"",F44-Config!$B$5)</f>
         <v>16</v>
       </c>
-      <c r="H38" s="31" t="str">
-        <f>IF(Config!$A$27="","",IF(AND(B38&gt;0,C38&gt;=B38),"Concluída",IF(AND(F38&lt;&gt;"",F38&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
+      <c r="H44" s="31" t="str">
+        <f>IF(Config!$A$27="","",IF(AND(B44&gt;0,C44&gt;=B44),"Concluída",IF(AND(F44&lt;&gt;"",F44&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
         <v>Em andamento</v>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="35" t="str">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="35" t="str">
         <f>IF(Config!$A$28="","",Config!$A$28)</f>
-        <v>Conta de provisão de impostos com o saldo da planilha 10</v>
-      </c>
-      <c r="B39" s="28">
+        <v>Conta de provisão de impostos com o saldo de agosto (planilha 10)</v>
+      </c>
+      <c r="B45" s="28">
         <f>IF(Config!$A$28="","",Config!$B$28)</f>
-        <v>21937</v>
-      </c>
-      <c r="C39" s="28">
+        <v>17527</v>
+      </c>
+      <c r="C45" s="28">
         <f>IF(Config!$A$28="","",Config!$C$28)</f>
         <v>17500</v>
       </c>
-      <c r="D39" s="30">
-        <f>IF(OR(Config!$A$28="",B39=0),"",MIN(1,C39/B39))</f>
-        <v>0.797738979805808</v>
-      </c>
-      <c r="E39" s="32" t="str">
-        <f>IF(D39="","",REPT("█",ROUND(D39*20,0)))</f>
-        <v>████████████████</v>
-      </c>
-      <c r="F39" s="36">
+      <c r="D45" s="30">
+        <f>IF(OR(Config!$A$28="",B45=0),"",MIN(1,C45/B45))</f>
+        <v>0.998459519598334</v>
+      </c>
+      <c r="E45" s="32" t="str">
+        <f>IF(D45="","",REPT("█",ROUND(D45*20,0)))</f>
+        <v>████████████████████</v>
+      </c>
+      <c r="F45" s="36">
         <f>IF(OR(Config!$A$28="",Config!$D$28=""),"",Config!$D$28)</f>
         <v>46295.0</v>
       </c>
-      <c r="G39" s="37">
-        <f>IF(OR(Config!$A$28="",F39="",H39="Concluída"),"",F39-Config!$B$5)</f>
+      <c r="G45" s="37">
+        <f>IF(OR(Config!$A$28="",F45="",H45="Concluída"),"",F45-Config!$B$5)</f>
         <v>16</v>
       </c>
-      <c r="H39" s="31" t="str">
-        <f>IF(Config!$A$28="","",IF(AND(B39&gt;0,C39&gt;=B39),"Concluída",IF(AND(F39&lt;&gt;"",F39&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
+      <c r="H45" s="31" t="str">
+        <f>IF(Config!$A$28="","",IF(AND(B45&gt;0,C45&gt;=B45),"Concluída",IF(AND(F45&lt;&gt;"",F45&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
         <v>Em andamento</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>Atualize o valor atual das metas em Config toda sexta. Prazo vencido não é fracasso: é sinal para renegociar a meta ou o aporte com o sócio.</t>
         </is>
@@ -2329,17 +2545,19 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="43">
+  <mergeCells count="49">
+    <mergeCell ref="G38:I38"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G28:I28"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G37:I37"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="G30:I30"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="G33:I33"/>
@@ -2348,7 +2566,7 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="G35:I35"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="G26:I26"/>
     <mergeCell ref="G29:I29"/>
@@ -2365,12 +2583,16 @@
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="G21:I21"/>
+    <mergeCell ref="A41:J41"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A46:J46"/>
     <mergeCell ref="I4:J4"/>
+    <mergeCell ref="G36:I36"/>
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G39:I39"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
@@ -2385,20 +2607,20 @@
       <formula>LEFT(B7,5)="Verde"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10:F33">
+  <conditionalFormatting sqref="A10:F39">
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>$F10="Meta atingida"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H37:H39">
+  <conditionalFormatting sqref="H43:H45">
     <cfRule type="expression" priority="5" dxfId="3">
-      <formula>H37="Concluída"</formula>
+      <formula>H43="Concluída"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="4">
-      <formula>H37="Prazo vencido"</formula>
+      <formula>H43="Prazo vencido"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="5">
-      <formula>H37="Em andamento"</formula>
+      <formula>H43="Em andamento"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2412,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2504,18 +2726,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Meta de reserva (meses de custo fixo)</t>
+          <t>Meta de reserva (meses de custo fixo + pró-labore)</t>
         </is>
       </c>
       <c r="B8" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>Três meses de custo fixo é a meta usual para uma clínica pequena: convênio atrasa, agenda esvazia em janeiro e julho, equipamento quebra.</t>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>Três meses do que a clínica paga todo mês mesmo parada — custo fixo MAIS o pró-labore dos sócios — é a meta usual para uma clínica pequena: convênio atrasa, agenda esvazia em janeiro e julho, equipamento quebra. Atenção ao nome: "custo fixo" nas planilhas 05, 09 e 18 é só a estrutura (R$ 10.000 no exemplo); aqui é custo fixo + pró-labore (R$ 28.000 num mês sem retirada extra).</t>
         </is>
       </c>
       <c r="H8" s="39" t="inlineStr">
@@ -2530,7 +2752,7 @@
           <t>Aporte mensal planejado para a reserva</t>
         </is>
       </c>
-      <c r="B9" s="42" t="n">
+      <c r="B9" s="43" t="n">
         <v>3000</v>
       </c>
       <c r="H9" s="39" t="inlineStr">
@@ -2549,7 +2771,7 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Custo fixo dos últimos 3 meses (com pró-labore fixo)</t>
+          <t>Custo fixo + pró-labore dos últimos 3 meses (o que sai todo mês, mesmo com a agenda vazia)</t>
         </is>
       </c>
       <c r="H11" s="39" t="inlineStr">
@@ -2566,7 +2788,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Custo fixo do mês</t>
+          <t>Custo fixo + pró-labore do mês</t>
         </is>
       </c>
       <c r="H12" s="39" t="inlineStr">
@@ -2581,12 +2803,12 @@
           <t>Junho</t>
         </is>
       </c>
-      <c r="B13" s="42" t="n">
-        <v>28000</v>
-      </c>
-      <c r="D13" s="43" t="inlineStr">
-        <is>
-          <t>Copie de "Para onde foi o dinheiro" (Painel da planilha 09): aluguel, recepção, contador, sistema, energia, limpeza, marketing, anuidades e pró-labore fixo. Impostos, materiais, taxas de cartão e repasse ficam fora (variam com o movimento).</t>
+      <c r="B13" s="43" t="n">
+        <v>29500</v>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>Copie de "Para onde foi o dinheiro" (Painel da planilha 09), somando as oito linhas de custo fixo (aluguel, recepção, contador, sistema, energia, limpeza, marketing, anuidades) com a linha "Pró-labore dos sócios" inteira, como ela aparece lá. Impostos, materiais, taxas de cartão e repasse ficam fora (variam com o movimento). No exemplo: junho R$ 29.500 e julho R$ 31.591 vêm acima dos R$ 28.000 de agosto porque a linha de pró-labore da 09 traz também a retirada extra de 19/06 e a distribuição de lucro paga em 10/07 — a média fica um pouco acima do mês normal, e a meta de reserva sai mais conservadora. Se preferir dimensionar pelo mês normal, use os três meses sem retirada extra.</t>
         </is>
       </c>
       <c r="H13" s="39" t="inlineStr">
@@ -2601,8 +2823,8 @@
           <t>Julho</t>
         </is>
       </c>
-      <c r="B14" s="42" t="n">
-        <v>28000</v>
+      <c r="B14" s="43" t="n">
+        <v>31697</v>
       </c>
       <c r="H14" s="39" t="inlineStr">
         <is>
@@ -2616,7 +2838,7 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="B15" s="42" t="n">
+      <c r="B15" s="43" t="n">
         <v>28000</v>
       </c>
       <c r="H15" s="39" t="inlineStr">
@@ -2628,12 +2850,12 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>Custo fixo médio</t>
+          <t>Custo fixo + pró-labore médio</t>
         </is>
       </c>
       <c r="B16" s="44">
         <f>IFERROR(AVERAGE(B13:B15),0)</f>
-        <v>28000</v>
+        <v>29732.3333333333</v>
       </c>
       <c r="H16" s="39" t="inlineStr">
         <is>
@@ -2654,8 +2876,8 @@
           <t>Saldo em caixa da clínica (conta corrente)</t>
         </is>
       </c>
-      <c r="B19" s="42" t="n">
-        <v>52251.29</v>
+      <c r="B19" s="43" t="n">
+        <v>52758.29</v>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
@@ -2669,8 +2891,8 @@
           <t>Compromissos já lançados e ainda não pagos</t>
         </is>
       </c>
-      <c r="B20" s="42" t="n">
-        <v>25997</v>
+      <c r="B20" s="43" t="n">
+        <v>25922</v>
       </c>
     </row>
     <row r="21">
@@ -2681,7 +2903,7 @@
       </c>
       <c r="B21" s="45">
         <f>B19-B20</f>
-        <v>26254.29</v>
+        <v>26836.29</v>
       </c>
     </row>
     <row r="22">
@@ -2690,7 +2912,7 @@
           <t>Reserva já guardada (conta separada)</t>
         </is>
       </c>
-      <c r="B22" s="42" t="n">
+      <c r="B22" s="43" t="n">
         <v>14000</v>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -2731,13 +2953,13 @@
     <row r="26">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>Reserva com 1 mês de custo fixo</t>
-        </is>
-      </c>
-      <c r="B26" s="42" t="n">
+          <t>Reserva com 1 mês de custo fixo + pró-labore</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="n">
         <v>28000</v>
       </c>
-      <c r="C26" s="42" t="n">
+      <c r="C26" s="43" t="n">
         <v>14000</v>
       </c>
       <c r="D26" s="46" t="n">
@@ -2750,11 +2972,11 @@
           <t>Receber R$ 130.000 no trimestre</t>
         </is>
       </c>
-      <c r="B27" s="42" t="n">
+      <c r="B27" s="43" t="n">
         <v>130000</v>
       </c>
-      <c r="C27" s="42" t="n">
-        <v>125007</v>
+      <c r="C27" s="43" t="n">
+        <v>125032</v>
       </c>
       <c r="D27" s="46" t="n">
         <v>46295</v>
@@ -2763,13 +2985,13 @@
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t>Conta de provisão de impostos com o saldo da planilha 10</t>
-        </is>
-      </c>
-      <c r="B28" s="42" t="n">
-        <v>21937</v>
-      </c>
-      <c r="C28" s="42" t="n">
+          <t>Conta de provisão de impostos com o saldo de agosto (planilha 10)</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="n">
+        <v>17527</v>
+      </c>
+      <c r="C28" s="43" t="n">
         <v>17500</v>
       </c>
       <c r="D28" s="46" t="n">
@@ -2777,7 +2999,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="22" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Metas que se medem em reais e crescem até o alvo (reserva, recebimentos, provisão separada). Atualize o valor atual toda sexta. No exemplo os prazos são datas fixas (fim do trimestre e do ano).</t>
         </is>
@@ -2785,8 +3010,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="3">
-    <mergeCell ref="D13:F15"/>
+  <mergeCells count="4">
+    <mergeCell ref="D8:F9"/>
+    <mergeCell ref="D13:F16"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G7" s="22" t="str">
         <f>"Contando o caixa livre (R$ "&amp;FIXED(Config!$B$21,0)&amp;"): "&amp;FIXED(IF(Config!$B$16=0,0,(C5+Config!$B$21)/Config!$B$16),1)&amp;" meses"</f>
-        <v>Contando o caixa livre (R$ 26,836): 1.4 meses</v>
+        <v>Contando o caixa livre (R$ 26.836): 1,4 meses</v>
       </c>
     </row>
     <row r="8">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
@@ -18,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -272,16 +273,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -299,10 +300,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -312,7 +313,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -321,7 +322,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -342,16 +343,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -947,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1120,17 +1121,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1212,7 +1225,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>Config!$B$8*Config!$B$16</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
@@ -1222,12 +1235,12 @@
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>MAX(0,A5-C5)</f>
-        <v>75197</v>
+        <v>77909</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>IF(Config!$B$16=0,0,C5/Config!$B$16)</f>
-        <v>0.470867854300033</v>
+        <v>0.456973745770273</v>
       </c>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="19" t="str">
@@ -1249,7 +1262,7 @@
       </c>
       <c r="G7" s="22" t="str">
         <f>"Contando o caixa livre (R$ "&amp;FIXED(Config!$B$21,0)&amp;"): "&amp;FIXED(IF(Config!$B$16=0,0,(C5+Config!$B$21)/Config!$B$16),1)&amp;" meses"</f>
-        <v>Contando o caixa livre (R$ 26.836): 1,4 meses</v>
+        <v>Contando o caixa livre (R$ 12.003): 0,8 meses</v>
       </c>
     </row>
     <row r="8">
@@ -1317,7 +1330,7 @@
       </c>
       <c r="E10" s="30">
         <f>IF($A$5=0,"",D10/$A$5)</f>
-        <v>0.190589369597632</v>
+        <v>0.184965563764158</v>
       </c>
       <c r="F10" s="31">
         <f>IF(D10&gt;=$A$5,IF(B10&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1331,7 +1344,7 @@
       <c r="I10" s="26" t="n"/>
       <c r="J10" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="11">
@@ -1353,7 +1366,7 @@
       </c>
       <c r="E11" s="30">
         <f>IF($A$5=0,"",D11/$A$5)</f>
-        <v>0.22422278776192</v>
+        <v>0.217606545604892</v>
       </c>
       <c r="F11" s="31">
         <f>IF(D11&gt;=$A$5,IF(B11&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1367,7 +1380,7 @@
       <c r="I11" s="26" t="n"/>
       <c r="J11" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="12">
@@ -1389,7 +1402,7 @@
       </c>
       <c r="E12" s="30">
         <f>IF($A$5=0,"",D12/$A$5)</f>
-        <v>0.257856205926208</v>
+        <v>0.250247527445626</v>
       </c>
       <c r="F12" s="31">
         <f>IF(D12&gt;=$A$5,IF(B12&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1403,7 +1416,7 @@
       <c r="I12" s="26" t="n"/>
       <c r="J12" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="13">
@@ -1425,7 +1438,7 @@
       </c>
       <c r="E13" s="30">
         <f>IF($A$5=0,"",D13/$A$5)</f>
-        <v>0.291489624090496</v>
+        <v>0.282888509286359</v>
       </c>
       <c r="F13" s="31">
         <f>IF(D13&gt;=$A$5,IF(B13&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1433,13 +1446,13 @@
       </c>
       <c r="G13" s="32" t="str">
         <f>IF(E13="","",REPT("█",ROUND(MIN(1,E13)*30,0)))</f>
-        <v>█████████</v>
+        <v>████████</v>
       </c>
       <c r="H13" s="25" t="n"/>
       <c r="I13" s="26" t="n"/>
       <c r="J13" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="14">
@@ -1461,7 +1474,7 @@
       </c>
       <c r="E14" s="30">
         <f>IF($A$5=0,"",D14/$A$5)</f>
-        <v>0.325123042254784</v>
+        <v>0.315529491127093</v>
       </c>
       <c r="F14" s="31">
         <f>IF(D14&gt;=$A$5,IF(B14&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1469,13 +1482,13 @@
       </c>
       <c r="G14" s="32" t="str">
         <f>IF(E14="","",REPT("█",ROUND(MIN(1,E14)*30,0)))</f>
-        <v>██████████</v>
+        <v>█████████</v>
       </c>
       <c r="H14" s="25" t="n"/>
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="15">
@@ -1497,7 +1510,7 @@
       </c>
       <c r="E15" s="30">
         <f>IF($A$5=0,"",D15/$A$5)</f>
-        <v>0.358756460419072</v>
+        <v>0.348170472967827</v>
       </c>
       <c r="F15" s="31">
         <f>IF(D15&gt;=$A$5,IF(B15&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1505,13 +1518,13 @@
       </c>
       <c r="G15" s="32" t="str">
         <f>IF(E15="","",REPT("█",ROUND(MIN(1,E15)*30,0)))</f>
-        <v>███████████</v>
+        <v>██████████</v>
       </c>
       <c r="H15" s="25" t="n"/>
       <c r="I15" s="26" t="n"/>
       <c r="J15" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="16">
@@ -1533,7 +1546,7 @@
       </c>
       <c r="E16" s="30">
         <f>IF($A$5=0,"",D16/$A$5)</f>
-        <v>0.39238987858336</v>
+        <v>0.380811454808561</v>
       </c>
       <c r="F16" s="31">
         <f>IF(D16&gt;=$A$5,IF(B16&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1541,13 +1554,13 @@
       </c>
       <c r="G16" s="32" t="str">
         <f>IF(E16="","",REPT("█",ROUND(MIN(1,E16)*30,0)))</f>
-        <v>████████████</v>
+        <v>███████████</v>
       </c>
       <c r="H16" s="25" t="n"/>
       <c r="I16" s="26" t="n"/>
       <c r="J16" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="17">
@@ -1569,7 +1582,7 @@
       </c>
       <c r="E17" s="30">
         <f>IF($A$5=0,"",D17/$A$5)</f>
-        <v>0.426023296747648</v>
+        <v>0.413452436649294</v>
       </c>
       <c r="F17" s="31">
         <f>IF(D17&gt;=$A$5,IF(B17&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1577,13 +1590,13 @@
       </c>
       <c r="G17" s="32" t="str">
         <f>IF(E17="","",REPT("█",ROUND(MIN(1,E17)*30,0)))</f>
-        <v>█████████████</v>
+        <v>████████████</v>
       </c>
       <c r="H17" s="25" t="n"/>
       <c r="I17" s="26" t="n"/>
       <c r="J17" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="18">
@@ -1605,7 +1618,7 @@
       </c>
       <c r="E18" s="30">
         <f>IF($A$5=0,"",D18/$A$5)</f>
-        <v>0.459656714911937</v>
+        <v>0.446093418490028</v>
       </c>
       <c r="F18" s="31">
         <f>IF(D18&gt;=$A$5,IF(B18&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1613,13 +1626,13 @@
       </c>
       <c r="G18" s="32" t="str">
         <f>IF(E18="","",REPT("█",ROUND(MIN(1,E18)*30,0)))</f>
-        <v>██████████████</v>
+        <v>█████████████</v>
       </c>
       <c r="H18" s="25" t="n"/>
       <c r="I18" s="26" t="n"/>
       <c r="J18" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="19">
@@ -1641,7 +1654,7 @@
       </c>
       <c r="E19" s="30">
         <f>IF($A$5=0,"",D19/$A$5)</f>
-        <v>0.493290133076225</v>
+        <v>0.478734400330762</v>
       </c>
       <c r="F19" s="31">
         <f>IF(D19&gt;=$A$5,IF(B19&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1649,13 +1662,13 @@
       </c>
       <c r="G19" s="32" t="str">
         <f>IF(E19="","",REPT("█",ROUND(MIN(1,E19)*30,0)))</f>
-        <v>███████████████</v>
+        <v>██████████████</v>
       </c>
       <c r="H19" s="25" t="n"/>
       <c r="I19" s="26" t="n"/>
       <c r="J19" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="20">
@@ -1677,7 +1690,7 @@
       </c>
       <c r="E20" s="30">
         <f>IF($A$5=0,"",D20/$A$5)</f>
-        <v>0.526923551240513</v>
+        <v>0.511375382171496</v>
       </c>
       <c r="F20" s="31">
         <f>IF(D20&gt;=$A$5,IF(B20&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1685,13 +1698,13 @@
       </c>
       <c r="G20" s="32" t="str">
         <f>IF(E20="","",REPT("█",ROUND(MIN(1,E20)*30,0)))</f>
-        <v>████████████████</v>
+        <v>███████████████</v>
       </c>
       <c r="H20" s="25" t="n"/>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="21">
@@ -1713,7 +1726,7 @@
       </c>
       <c r="E21" s="30">
         <f>IF($A$5=0,"",D21/$A$5)</f>
-        <v>0.560556969404801</v>
+        <v>0.54401636401223</v>
       </c>
       <c r="F21" s="31">
         <f>IF(D21&gt;=$A$5,IF(B21&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1721,13 +1734,13 @@
       </c>
       <c r="G21" s="32" t="str">
         <f>IF(E21="","",REPT("█",ROUND(MIN(1,E21)*30,0)))</f>
-        <v>█████████████████</v>
+        <v>████████████████</v>
       </c>
       <c r="H21" s="25" t="n"/>
       <c r="I21" s="26" t="n"/>
       <c r="J21" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="22">
@@ -1749,7 +1762,7 @@
       </c>
       <c r="E22" s="30">
         <f>IF($A$5=0,"",D22/$A$5)</f>
-        <v>0.594190387569089</v>
+        <v>0.576657345852963</v>
       </c>
       <c r="F22" s="31">
         <f>IF(D22&gt;=$A$5,IF(B22&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1757,13 +1770,13 @@
       </c>
       <c r="G22" s="32" t="str">
         <f>IF(E22="","",REPT("█",ROUND(MIN(1,E22)*30,0)))</f>
-        <v>██████████████████</v>
+        <v>█████████████████</v>
       </c>
       <c r="H22" s="25" t="n"/>
       <c r="I22" s="26" t="n"/>
       <c r="J22" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="23">
@@ -1785,7 +1798,7 @@
       </c>
       <c r="E23" s="30">
         <f>IF($A$5=0,"",D23/$A$5)</f>
-        <v>0.627823805733377</v>
+        <v>0.609298327693697</v>
       </c>
       <c r="F23" s="31">
         <f>IF(D23&gt;=$A$5,IF(B23&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1793,13 +1806,13 @@
       </c>
       <c r="G23" s="32" t="str">
         <f>IF(E23="","",REPT("█",ROUND(MIN(1,E23)*30,0)))</f>
-        <v>███████████████████</v>
+        <v>██████████████████</v>
       </c>
       <c r="H23" s="25" t="n"/>
       <c r="I23" s="26" t="n"/>
       <c r="J23" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="24">
@@ -1821,7 +1834,7 @@
       </c>
       <c r="E24" s="30">
         <f>IF($A$5=0,"",D24/$A$5)</f>
-        <v>0.661457223897665</v>
+        <v>0.641939309534431</v>
       </c>
       <c r="F24" s="31">
         <f>IF(D24&gt;=$A$5,IF(B24&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1829,13 +1842,13 @@
       </c>
       <c r="G24" s="32" t="str">
         <f>IF(E24="","",REPT("█",ROUND(MIN(1,E24)*30,0)))</f>
-        <v>████████████████████</v>
+        <v>███████████████████</v>
       </c>
       <c r="H24" s="25" t="n"/>
       <c r="I24" s="26" t="n"/>
       <c r="J24" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="25">
@@ -1857,7 +1870,7 @@
       </c>
       <c r="E25" s="30">
         <f>IF($A$5=0,"",D25/$A$5)</f>
-        <v>0.695090642061953</v>
+        <v>0.674580291375165</v>
       </c>
       <c r="F25" s="31">
         <f>IF(D25&gt;=$A$5,IF(B25&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1865,13 +1878,13 @@
       </c>
       <c r="G25" s="32" t="str">
         <f>IF(E25="","",REPT("█",ROUND(MIN(1,E25)*30,0)))</f>
-        <v>█████████████████████</v>
+        <v>████████████████████</v>
       </c>
       <c r="H25" s="25" t="n"/>
       <c r="I25" s="26" t="n"/>
       <c r="J25" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="26">
@@ -1893,7 +1906,7 @@
       </c>
       <c r="E26" s="30">
         <f>IF($A$5=0,"",D26/$A$5)</f>
-        <v>0.728724060226241</v>
+        <v>0.707221273215898</v>
       </c>
       <c r="F26" s="31">
         <f>IF(D26&gt;=$A$5,IF(B26&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1901,13 +1914,13 @@
       </c>
       <c r="G26" s="32" t="str">
         <f>IF(E26="","",REPT("█",ROUND(MIN(1,E26)*30,0)))</f>
-        <v>██████████████████████</v>
+        <v>█████████████████████</v>
       </c>
       <c r="H26" s="25" t="n"/>
       <c r="I26" s="26" t="n"/>
       <c r="J26" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="27">
@@ -1929,7 +1942,7 @@
       </c>
       <c r="E27" s="30">
         <f>IF($A$5=0,"",D27/$A$5)</f>
-        <v>0.762357478390529</v>
+        <v>0.739862255056632</v>
       </c>
       <c r="F27" s="31">
         <f>IF(D27&gt;=$A$5,IF(B27&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1937,13 +1950,13 @@
       </c>
       <c r="G27" s="32" t="str">
         <f>IF(E27="","",REPT("█",ROUND(MIN(1,E27)*30,0)))</f>
-        <v>███████████████████████</v>
+        <v>██████████████████████</v>
       </c>
       <c r="H27" s="25" t="n"/>
       <c r="I27" s="26" t="n"/>
       <c r="J27" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="28">
@@ -1965,7 +1978,7 @@
       </c>
       <c r="E28" s="30">
         <f>IF($A$5=0,"",D28/$A$5)</f>
-        <v>0.795990896554817</v>
+        <v>0.772503236897366</v>
       </c>
       <c r="F28" s="31">
         <f>IF(D28&gt;=$A$5,IF(B28&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -1973,13 +1986,13 @@
       </c>
       <c r="G28" s="32" t="str">
         <f>IF(E28="","",REPT("█",ROUND(MIN(1,E28)*30,0)))</f>
-        <v>████████████████████████</v>
+        <v>███████████████████████</v>
       </c>
       <c r="H28" s="25" t="n"/>
       <c r="I28" s="26" t="n"/>
       <c r="J28" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="29">
@@ -2001,7 +2014,7 @@
       </c>
       <c r="E29" s="30">
         <f>IF($A$5=0,"",D29/$A$5)</f>
-        <v>0.829624314719105</v>
+        <v>0.8051442187381</v>
       </c>
       <c r="F29" s="31">
         <f>IF(D29&gt;=$A$5,IF(B29&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2009,13 +2022,13 @@
       </c>
       <c r="G29" s="32" t="str">
         <f>IF(E29="","",REPT("█",ROUND(MIN(1,E29)*30,0)))</f>
-        <v>█████████████████████████</v>
+        <v>████████████████████████</v>
       </c>
       <c r="H29" s="25" t="n"/>
       <c r="I29" s="26" t="n"/>
       <c r="J29" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="30">
@@ -2037,7 +2050,7 @@
       </c>
       <c r="E30" s="30">
         <f>IF($A$5=0,"",D30/$A$5)</f>
-        <v>0.863257732883393</v>
+        <v>0.837785200578833</v>
       </c>
       <c r="F30" s="31">
         <f>IF(D30&gt;=$A$5,IF(B30&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2045,13 +2058,13 @@
       </c>
       <c r="G30" s="32" t="str">
         <f>IF(E30="","",REPT("█",ROUND(MIN(1,E30)*30,0)))</f>
-        <v>██████████████████████████</v>
+        <v>█████████████████████████</v>
       </c>
       <c r="H30" s="25" t="n"/>
       <c r="I30" s="26" t="n"/>
       <c r="J30" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="31">
@@ -2073,7 +2086,7 @@
       </c>
       <c r="E31" s="30">
         <f>IF($A$5=0,"",D31/$A$5)</f>
-        <v>0.896891151047681</v>
+        <v>0.870426182419567</v>
       </c>
       <c r="F31" s="31">
         <f>IF(D31&gt;=$A$5,IF(B31&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2081,13 +2094,13 @@
       </c>
       <c r="G31" s="32" t="str">
         <f>IF(E31="","",REPT("█",ROUND(MIN(1,E31)*30,0)))</f>
-        <v>███████████████████████████</v>
+        <v>██████████████████████████</v>
       </c>
       <c r="H31" s="25" t="n"/>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="32">
@@ -2109,7 +2122,7 @@
       </c>
       <c r="E32" s="30">
         <f>IF($A$5=0,"",D32/$A$5)</f>
-        <v>0.930524569211969</v>
+        <v>0.903067164260301</v>
       </c>
       <c r="F32" s="31">
         <f>IF(D32&gt;=$A$5,IF(B32&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2117,13 +2130,13 @@
       </c>
       <c r="G32" s="32" t="str">
         <f>IF(E32="","",REPT("█",ROUND(MIN(1,E32)*30,0)))</f>
-        <v>████████████████████████████</v>
+        <v>███████████████████████████</v>
       </c>
       <c r="H32" s="25" t="n"/>
       <c r="I32" s="26" t="n"/>
       <c r="J32" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="33">
@@ -2145,7 +2158,7 @@
       </c>
       <c r="E33" s="30">
         <f>IF($A$5=0,"",D33/$A$5)</f>
-        <v>0.964157987376257</v>
+        <v>0.935708146101035</v>
       </c>
       <c r="F33" s="31">
         <f>IF(D33&gt;=$A$5,IF(B33&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2153,13 +2166,13 @@
       </c>
       <c r="G33" s="32" t="str">
         <f>IF(E33="","",REPT("█",ROUND(MIN(1,E33)*30,0)))</f>
-        <v>█████████████████████████████</v>
+        <v>████████████████████████████</v>
       </c>
       <c r="H33" s="25" t="n"/>
       <c r="I33" s="26" t="n"/>
       <c r="J33" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="34">
@@ -2181,7 +2194,7 @@
       </c>
       <c r="E34" s="30">
         <f>IF($A$5=0,"",D34/$A$5)</f>
-        <v>0.997791405540545</v>
+        <v>0.968349127941769</v>
       </c>
       <c r="F34" s="31">
         <f>IF(D34&gt;=$A$5,IF(B34&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2189,13 +2202,13 @@
       </c>
       <c r="G34" s="32" t="str">
         <f>IF(E34="","",REPT("█",ROUND(MIN(1,E34)*30,0)))</f>
-        <v>██████████████████████████████</v>
+        <v>█████████████████████████████</v>
       </c>
       <c r="H34" s="25" t="n"/>
       <c r="I34" s="26" t="n"/>
       <c r="J34" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="35">
@@ -2217,7 +2230,7 @@
       </c>
       <c r="E35" s="30">
         <f>IF($A$5=0,"",D35/$A$5)</f>
-        <v>1.03142482370483</v>
+        <v>1.0009901097825</v>
       </c>
       <c r="F35" s="31" t="str">
         <f>IF(D35&gt;=$A$5,IF(B35&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2231,7 +2244,7 @@
       <c r="I35" s="26" t="n"/>
       <c r="J35" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="36">
@@ -2253,7 +2266,7 @@
       </c>
       <c r="E36" s="30">
         <f>IF($A$5=0,"",D36/$A$5)</f>
-        <v>1.06505824186912</v>
+        <v>1.03363109162324</v>
       </c>
       <c r="F36" s="31" t="str">
         <f>IF(D36&gt;=$A$5,IF(B36&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2267,7 +2280,7 @@
       <c r="I36" s="26" t="n"/>
       <c r="J36" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="37">
@@ -2289,7 +2302,7 @@
       </c>
       <c r="E37" s="30">
         <f>IF($A$5=0,"",D37/$A$5)</f>
-        <v>1.09869166003341</v>
+        <v>1.06627207346397</v>
       </c>
       <c r="F37" s="31" t="str">
         <f>IF(D37&gt;=$A$5,IF(B37&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2303,7 +2316,7 @@
       <c r="I37" s="26" t="n"/>
       <c r="J37" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="38">
@@ -2325,7 +2338,7 @@
       </c>
       <c r="E38" s="30">
         <f>IF($A$5=0,"",D38/$A$5)</f>
-        <v>1.1323250781977</v>
+        <v>1.0989130553047</v>
       </c>
       <c r="F38" s="31" t="str">
         <f>IF(D38&gt;=$A$5,IF(B38&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2339,7 +2352,7 @@
       <c r="I38" s="26" t="n"/>
       <c r="J38" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="39">
@@ -2361,7 +2374,7 @@
       </c>
       <c r="E39" s="30">
         <f>IF($A$5=0,"",D39/$A$5)</f>
-        <v>1.16595849636199</v>
+        <v>1.13155403714544</v>
       </c>
       <c r="F39" s="31" t="str">
         <f>IF(D39&gt;=$A$5,IF(B39&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
@@ -2375,7 +2388,7 @@
       <c r="I39" s="26" t="n"/>
       <c r="J39" s="33">
         <f>$A$5</f>
-        <v>89197</v>
+        <v>91909</v>
       </c>
     </row>
     <row r="40">
@@ -2479,11 +2492,11 @@
       </c>
       <c r="C44" s="28">
         <f>IF(Config!$A$27="","",Config!$C$27)</f>
-        <v>125032</v>
+        <v>121022</v>
       </c>
       <c r="D44" s="30">
         <f>IF(OR(Config!$A$27="",B44=0),"",MIN(1,C44/B44))</f>
-        <v>0.961784615384615</v>
+        <v>0.930938461538462</v>
       </c>
       <c r="E44" s="32" t="str">
         <f>IF(D44="","",REPT("█",ROUND(D44*20,0)))</f>
@@ -2509,7 +2522,7 @@
       </c>
       <c r="B45" s="28">
         <f>IF(Config!$A$28="","",Config!$B$28)</f>
-        <v>17527</v>
+        <v>18209</v>
       </c>
       <c r="C45" s="28">
         <f>IF(Config!$A$28="","",Config!$C$28)</f>
@@ -2517,11 +2530,11 @@
       </c>
       <c r="D45" s="30">
         <f>IF(OR(Config!$A$28="",B45=0),"",MIN(1,C45/B45))</f>
-        <v>0.998459519598334</v>
+        <v>0.961063210500302</v>
       </c>
       <c r="E45" s="32" t="str">
         <f>IF(D45="","",REPT("█",ROUND(D45*20,0)))</f>
-        <v>████████████████████</v>
+        <v>███████████████████</v>
       </c>
       <c r="F45" s="36">
         <f>IF(OR(Config!$A$28="",Config!$D$28=""),"",Config!$D$28)</f>
@@ -2684,9 +2697,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B5" s="36">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="36" t="n">
+        <v>46279</v>
       </c>
       <c r="H5" s="39" t="inlineStr">
         <is>
@@ -2824,7 +2836,7 @@
         </is>
       </c>
       <c r="B14" s="43" t="n">
-        <v>31697</v>
+        <v>34409</v>
       </c>
       <c r="H14" s="39" t="inlineStr">
         <is>
@@ -2855,7 +2867,7 @@
       </c>
       <c r="B16" s="44">
         <f>IFERROR(AVERAGE(B13:B15),0)</f>
-        <v>29732.3333333333</v>
+        <v>30636.3333333333</v>
       </c>
       <c r="H16" s="39" t="inlineStr">
         <is>
@@ -2877,7 +2889,7 @@
         </is>
       </c>
       <c r="B19" s="43" t="n">
-        <v>52758.29</v>
+        <v>38605.81</v>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
@@ -2892,7 +2904,7 @@
         </is>
       </c>
       <c r="B20" s="43" t="n">
-        <v>25922</v>
+        <v>26603</v>
       </c>
     </row>
     <row r="21">
@@ -2903,7 +2915,7 @@
       </c>
       <c r="B21" s="45">
         <f>B19-B20</f>
-        <v>26836.29</v>
+        <v>12002.81</v>
       </c>
     </row>
     <row r="22">
@@ -2976,7 +2988,7 @@
         <v>130000</v>
       </c>
       <c r="C27" s="43" t="n">
-        <v>125032</v>
+        <v>121022</v>
       </c>
       <c r="D27" s="46" t="n">
         <v>46295</v>
@@ -2989,7 +3001,7 @@
         </is>
       </c>
       <c r="B28" s="43" t="n">
-        <v>17527</v>
+        <v>18209</v>
       </c>
       <c r="C28" s="43" t="n">
         <v>17500</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
@@ -3032,7 +3032,7 @@
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$H$5:$H$16</formula1>
     </dataValidation>
-    <dataValidation sqref="D26:D28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="D26:D28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>A frase "Contando o caixa livre" usa a função FIXED: os separadores seguem o idioma do Excel (em português: R$ 26.062 e 2,1 meses).</t>
+          <t>As frases do Painel montam os valores com TEXTO e FIXED, então os separadores seguem o idioma do Excel: milhar com ponto e decimal com vírgula em português. Os números vêm sempre das células; nenhum valor de exemplo está escrito dentro do texto.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2818,10 +2818,9 @@
       <c r="B13" s="43" t="n">
         <v>29500</v>
       </c>
-      <c r="D13" s="42" t="inlineStr">
-        <is>
-          <t>Copie de "Para onde foi o dinheiro" (Painel da planilha 09), somando as oito linhas de custo fixo (aluguel, recepção, contador, sistema, energia, limpeza, marketing, anuidades) com a linha "Pró-labore dos sócios" inteira, como ela aparece lá. Impostos, materiais, taxas de cartão e repasse ficam fora (variam com o movimento). No exemplo: junho R$ 29.500 e julho R$ 31.591 vêm acima dos R$ 28.000 de agosto porque a linha de pró-labore da 09 traz também a retirada extra de 19/06 e a distribuição de lucro paga em 10/07 — a média fica um pouco acima do mês normal, e a meta de reserva sai mais conservadora. Se preferir dimensionar pelo mês normal, use os três meses sem retirada extra.</t>
-        </is>
+      <c r="D13" s="42" t="str">
+        <f>"Copie de “Para onde foi o dinheiro” (Painel da planilha 09), somando as oito linhas de custo fixo (aluguel, recepção, contador, sistema, energia, limpeza, marketing, anuidades) com a linha “Pró-labore dos sócios” inteira, como ela aparece lá. Impostos, materiais, taxas de cartão e repasse ficam fora (variam com o movimento). No exemplo, "&amp;"R$ "&amp;FIXED($B$13,0)&amp;" em "&amp;$A$13&amp;" e "&amp;"R$ "&amp;FIXED($B$14,0)&amp;" em "&amp;$A$14&amp;" vêm acima dos "&amp;"R$ "&amp;FIXED($B$15,0)&amp;" de "&amp;$A$15&amp;": a linha de pró-labore da 09 traz também a retirada extra de 19/06 e a distribuição de lucro paga em 10/07, então a média fica um pouco acima do mês normal e a meta de reserva sai mais conservadora. Se preferir dimensionar pelo mês normal, use os três meses sem retirada extra."</f>
+        <v>Copie de “Para onde foi o dinheiro” (Painel da planilha 09), somando as oito linhas de custo fixo (aluguel, recepção, contador, sistema, energia, limpeza, marketing, anuidades) com a linha “Pró-labore dos sócios” inteira, como ela aparece lá. Impostos, materiais, taxas de cartão e repasse ficam fora (variam com o movimento). No exemplo, R$ 29.500 em Junho e R$ 34.409 em Julho vêm acima dos R$ 28.000 de Agosto: a linha de pró-labore da 09 traz também a retirada extra de 19/06 e a distribuição de lucro paga em 10/07, então a média fica um pouco acima do mês normal e a meta de reserva sai mais conservadora. Se preferir dimensionar pelo mês normal, use os três meses sem retirada extra.</v>
       </c>
       <c r="H13" s="39" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/12-reserva-e-metas-de-caixa.xlsx
@@ -2819,7 +2819,7 @@
         <v>29500</v>
       </c>
       <c r="D13" s="42" t="str">
-        <f>"Copie de “Para onde foi o dinheiro” (Painel da planilha 09), somando as oito linhas de custo fixo (aluguel, recepção, contador, sistema, energia, limpeza, marketing, anuidades) com a linha “Pró-labore dos sócios” inteira, como ela aparece lá. Impostos, materiais, taxas de cartão e repasse ficam fora (variam com o movimento). No exemplo, "&amp;"R$ "&amp;FIXED($B$13,0)&amp;" em "&amp;$A$13&amp;" e "&amp;"R$ "&amp;FIXED($B$14,0)&amp;" em "&amp;$A$14&amp;" vêm acima dos "&amp;"R$ "&amp;FIXED($B$15,0)&amp;" de "&amp;$A$15&amp;": a linha de pró-labore da 09 traz também a retirada extra de 19/06 e a distribuição de lucro paga em 10/07, então a média fica um pouco acima do mês normal e a meta de reserva sai mais conservadora. Se preferir dimensionar pelo mês normal, use os três meses sem retirada extra."</f>
+        <f>"Copie de “Para onde foi o dinheiro” (Painel da planilha 09), somando as oito linhas de custo fixo (aluguel, recepção, contador, sistema, energia, limpeza, marketing, anuidades) com a linha “Pró-labore dos sócios” inteira, como ela aparece lá. "&amp;"Impostos, materiais, taxas de cartão e repasse ficam fora (variam com o movimento). No exemplo, "&amp;"R$ "&amp;FIXED($B$13,0)&amp;" em "&amp;$A$13&amp;" e "&amp;"R$ "&amp;FIXED($B$14,0)&amp;" em "&amp;$A$14&amp;" vêm acima dos "&amp;"R$ "&amp;FIXED($B$15,0)&amp;" de "&amp;$A$15&amp;": a linha de pró-labore da 09 traz também a retirada extra de 19/06 e a distribuição de lucro paga em 10/07, "&amp;"então a média fica um pouco acima do mês normal e a meta de reserva sai mais conservadora. Se preferir dimensionar pelo mês normal, use os três meses sem retirada extra."</f>
         <v>Copie de “Para onde foi o dinheiro” (Painel da planilha 09), somando as oito linhas de custo fixo (aluguel, recepção, contador, sistema, energia, limpeza, marketing, anuidades) com a linha “Pró-labore dos sócios” inteira, como ela aparece lá. Impostos, materiais, taxas de cartão e repasse ficam fora (variam com o movimento). No exemplo, R$ 29.500 em Junho e R$ 34.409 em Julho vêm acima dos R$ 28.000 de Agosto: a linha de pró-labore da 09 traz também a retirada extra de 19/06 e a distribuição de lucro paga em 10/07, então a média fica um pouco acima do mês normal e a meta de reserva sai mais conservadora. Se preferir dimensionar pelo mês normal, use os três meses sem retirada extra.</v>
       </c>
       <c r="H13" s="39" t="inlineStr">
